--- a/batch-2026-11.xlsx
+++ b/batch-2026-11.xlsx
@@ -452,12 +452,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -479,12 +479,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -506,12 +506,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -602,12 +602,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -645,12 +645,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -688,12 +688,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="F4" t="n">
